--- a/output/Tables/2019/Monte Carlo/1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>7714.434235448246</v>
+        <v>7732.159631566338</v>
       </c>
       <c r="B2">
-        <v>8062.459299917082</v>
+        <v>8070.569293296523</v>
       </c>
       <c r="C2">
-        <v>8478.447377801487</v>
+        <v>8473.585452643467</v>
       </c>
       <c r="D2">
-        <v>5.51582047834551</v>
+        <v>5.528494136569946</v>
       </c>
       <c r="E2">
-        <v>5.76465839944073</v>
+        <v>5.77045704470703</v>
       </c>
       <c r="F2">
-        <v>6.06208987512808</v>
+        <v>6.058613598640097</v>
       </c>
       <c r="G2">
-        <v>68.94775597931888</v>
+        <v>69.10617670712432</v>
       </c>
       <c r="H2">
-        <v>72.05822999300912</v>
+        <v>72.13071305883788</v>
       </c>
       <c r="I2">
-        <v>75.776123439101</v>
+        <v>75.73266998300122</v>
       </c>
       <c r="J2">
         <v>1</v>

--- a/output/Tables/2019/Monte Carlo/1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>7732.159631566338</v>
+        <v>7725.358924692028</v>
       </c>
       <c r="B2">
-        <v>8070.569293296523</v>
+        <v>8063.70906096553</v>
       </c>
       <c r="C2">
-        <v>8473.585452643467</v>
+        <v>8466.6840321455</v>
       </c>
       <c r="D2">
-        <v>5.528494136569946</v>
+        <v>5.523631631154815</v>
       </c>
       <c r="E2">
-        <v>5.77045704470703</v>
+        <v>5.76555197859037</v>
       </c>
       <c r="F2">
-        <v>6.058613598640097</v>
+        <v>6.05367908298405</v>
       </c>
       <c r="G2">
-        <v>69.10617670712432</v>
+        <v>69.04539538943519</v>
       </c>
       <c r="H2">
-        <v>72.13071305883788</v>
+        <v>72.06939973237964</v>
       </c>
       <c r="I2">
-        <v>75.73266998300122</v>
+        <v>75.67098853730063</v>
       </c>
       <c r="J2">
         <v>1</v>
